--- a/data/navigation_updated.xlsx
+++ b/data/navigation_updated.xlsx
@@ -1,15 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="locations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="paths" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,32 +429,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name_AR</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name_EN</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Node_ID</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>StartPoint</t>
         </is>
@@ -693,12 +703,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>قاعة 1</t>
+          <t>قاعة E-301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Classroom 1</t>
+          <t>E-301</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -723,12 +733,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>قاعة 2</t>
+          <t>قاعة E-302</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Classroom 2</t>
+          <t>E-302</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -753,12 +763,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>قاعة 3</t>
+          <t>قاعة E-303</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Classroom 3</t>
+          <t>E-303</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -783,16 +793,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>معمل 1</t>
+          <t>معمل المشين</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lab 1</t>
+          <t>Machine Lab</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -813,12 +823,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>معمل 2</t>
+          <t>معمل الإلكترونيات</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lab 2</t>
+          <t>Electronics Lab</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -837,365 +847,6 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>FromNode</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ToNode</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>N001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>N002</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>forward</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>N002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>N004</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>forward</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>N002</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>N005</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>N002</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>N101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>N101</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>N201</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>N201</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>N202</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>forward</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>N202</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>N203</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>forward</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>N203</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>N204</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>N204</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>N205</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>forward</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>N205</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>N206</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>forward</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Keyword</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>TargetNode</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>library</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>N004</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>المكتبة</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>N004</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>pi</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>N005</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cafe</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>N005</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>مقهى</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>N005</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>malek</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>N201</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>مالك</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>N201</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>مهند</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>N202</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>muhannad</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>N202</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>جوهر</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>N203</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>jawhar</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>N203</t>
         </is>
       </c>
     </row>
